--- a/2Bat - Unitats i feina Classroom.xlsx
+++ b/2Bat - Unitats i feina Classroom.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>setmana</t>
   </si>
@@ -99,25 +99,82 @@
     <t>84, 108, 123, 124</t>
   </si>
   <si>
+    <t>12, 13, 15, 16, 17</t>
+  </si>
+  <si>
     <t>Matrius</t>
   </si>
   <si>
+    <t>42, 49, 69, 81, 85</t>
+  </si>
+  <si>
+    <t>35, 36, 37, 41, 44</t>
+  </si>
+  <si>
     <t>Determinants</t>
   </si>
   <si>
+    <t>79, 80, 83, 87</t>
+  </si>
+  <si>
+    <t>95, 96, 99, 100</t>
+  </si>
+  <si>
+    <t>38, 41, 42, 39, 43</t>
+  </si>
+  <si>
     <t>Sistemes d'equacions</t>
   </si>
   <si>
+    <t>55, 56</t>
+  </si>
+  <si>
+    <t>60, 64, 66</t>
+  </si>
+  <si>
+    <t>90, 92, 94, 100</t>
+  </si>
+  <si>
+    <t>43, 45, 46, 47, 49</t>
+  </si>
+  <si>
     <t>Rectes i plans en l'espai</t>
   </si>
   <si>
+    <t>53, 54, 55, 56, 59</t>
+  </si>
+  <si>
+    <t>63, 66, 71, 72, 73</t>
+  </si>
+  <si>
+    <t>74, 76, 77, 79</t>
+  </si>
+  <si>
+    <t>80, 81, 84, 85</t>
+  </si>
+  <si>
+    <t>74, 76, 86, 88</t>
+  </si>
+  <si>
     <t>Angles i distàncies a l'espai</t>
   </si>
   <si>
+    <t>90, 92, 97, 115, 139</t>
+  </si>
+  <si>
+    <t>52, 54</t>
+  </si>
+  <si>
     <t>Integrals indefinides</t>
   </si>
   <si>
+    <t>35, 39, 55, 79</t>
+  </si>
+  <si>
     <t>Integrals definides</t>
+  </si>
+  <si>
+    <t>80, 88, 96, 111, 114</t>
   </si>
 </sst>
 </file>
@@ -222,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -285,15 +342,6 @@
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -304,10 +352,13 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,7 +583,7 @@
     <col customWidth="1" min="5" max="5" width="21.25"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,9 +872,11 @@
       <c r="C19" s="11">
         <v>1.0</v>
       </c>
-      <c r="D19" s="22"/>
+      <c r="D19" s="12" t="s">
+        <v>28</v>
+      </c>
       <c r="E19" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -836,7 +889,9 @@
       <c r="C20" s="11">
         <v>1.0</v>
       </c>
-      <c r="D20" s="22"/>
+      <c r="D20" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9">
@@ -848,9 +903,11 @@
       <c r="C21" s="11">
         <v>2.0</v>
       </c>
-      <c r="D21" s="22"/>
+      <c r="D21" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="E21" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
@@ -863,7 +920,9 @@
       <c r="C22" s="11">
         <v>2.0</v>
       </c>
-      <c r="D22" s="22"/>
+      <c r="D22" s="12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15">
@@ -875,7 +934,9 @@
       <c r="C23" s="17">
         <v>2.0</v>
       </c>
-      <c r="D23" s="23"/>
+      <c r="D23" s="18" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="19">
@@ -887,9 +948,11 @@
       <c r="C24" s="6">
         <v>3.0</v>
       </c>
-      <c r="D24" s="24"/>
+      <c r="D24" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="E24" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
@@ -902,7 +965,9 @@
       <c r="C25" s="11">
         <v>3.0</v>
       </c>
-      <c r="D25" s="22"/>
+      <c r="D25" s="12" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9">
@@ -914,7 +979,9 @@
       <c r="C26" s="11">
         <v>3.0</v>
       </c>
-      <c r="D26" s="22"/>
+      <c r="D26" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9">
@@ -924,11 +991,10 @@
         <v>46460.0</v>
       </c>
       <c r="C27" s="11">
-        <v>5.0</v>
-      </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="8" t="s">
-        <v>31</v>
+        <v>3.0</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="28">
@@ -941,7 +1007,12 @@
       <c r="C28" s="11">
         <v>5.0</v>
       </c>
-      <c r="D28" s="22"/>
+      <c r="D28" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9">
@@ -953,7 +1024,9 @@
       <c r="C29" s="11">
         <v>5.0</v>
       </c>
-      <c r="D29" s="22"/>
+      <c r="D29" s="12" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9">
@@ -965,7 +1038,9 @@
       <c r="C30" s="11">
         <v>5.0</v>
       </c>
-      <c r="D30" s="22"/>
+      <c r="D30" s="12" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9">
@@ -977,7 +1052,9 @@
       <c r="C31" s="11">
         <v>5.0</v>
       </c>
-      <c r="D31" s="22"/>
+      <c r="D31" s="12" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9">
@@ -987,11 +1064,10 @@
         <v>46495.0</v>
       </c>
       <c r="C32" s="11">
-        <v>6.0</v>
-      </c>
-      <c r="D32" s="22"/>
-      <c r="E32" s="8" t="s">
-        <v>32</v>
+        <v>5.0</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="33">
@@ -1004,79 +1080,92 @@
       <c r="C33" s="11">
         <v>6.0</v>
       </c>
-      <c r="D33" s="22"/>
+      <c r="D33" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="25">
+      <c r="A34" s="22">
         <v>33.0</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="23">
         <v>46509.0</v>
       </c>
       <c r="C34" s="17">
-        <v>11.0</v>
-      </c>
-      <c r="D34" s="23"/>
-      <c r="E34" s="8" t="s">
-        <v>33</v>
+        <v>6.0</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11">
         <v>34.0</v>
       </c>
-      <c r="B35" s="27">
+      <c r="B35" s="24">
         <v>46516.0</v>
       </c>
       <c r="C35" s="11">
         <v>11.0</v>
       </c>
-      <c r="D35" s="28"/>
+      <c r="D35" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11">
         <v>35.0</v>
       </c>
-      <c r="B36" s="27">
+      <c r="B36" s="24">
         <v>46523.0</v>
       </c>
       <c r="C36" s="11">
         <v>12.0</v>
       </c>
-      <c r="D36" s="28"/>
+      <c r="D36" s="25" t="s">
+        <v>51</v>
+      </c>
       <c r="E36" s="8" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11">
         <v>36.0</v>
       </c>
-      <c r="B37" s="27">
+      <c r="B37" s="24">
         <v>46530.0</v>
       </c>
       <c r="C37" s="11">
         <v>12.0</v>
       </c>
-      <c r="D37" s="28"/>
+      <c r="D37" s="25" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="29"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="28"/>
+      <c r="A38" s="26"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="27"/>
     </row>
     <row r="39">
-      <c r="A39" s="29"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="28"/>
+      <c r="A39" s="26"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="27"/>
     </row>
     <row r="40">
-      <c r="A40" s="29"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="28"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="27"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
